--- a/docs/reports/custodes/Custodes-Better-Thing-2-Analysis-v1.0.xlsx
+++ b/docs/reports/custodes/Custodes-Better-Thing-2-Analysis-v1.0.xlsx
@@ -520,7 +520,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Prevalence-weighted win rate: ~52%.  FINDING: the biggest drag is the Purge-the-Foe matchups (Emperor's Children, T'au) — the matrix forces Priority-Assets Custodes onto Vital Link (hard) while they get Destroyer's Wrath. You out-fight them but lose the mission.</t>
+          <t>Prevalence-weighted win rate: ~54%.  FINDING: the biggest drag is the Purge-the-Foe matchups (Emperor's Children, T'au) — the matrix forces Priority-Assets Custodes onto Vital Link (hard) while they get Destroyer's Wrath. You out-fight them but lose the mission.</t>
         </is>
       </c>
     </row>
@@ -576,7 +576,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>52%</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -819,12 +819,12 @@
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>Lean favourable</t>
+          <t>Favourable</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Adeptus Mechanicus (59%), Necrons (55%), Adeptus Custodes (67%), Blood Angels (75%), Dark Angels (57%), Drukhari (74%), Astra Militarum (61%)</t>
+          <t>Adeptus Mechanicus (60%), Necrons (57%), Adeptus Custodes (66%), Blood Angels (78%), Dark Angels (57%), Drukhari (77%), Astra Militarum (62%)</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Emperor's Children (47%)</t>
+          <t>Emperor's Children (52%)</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Orks (31%), T'au Empire (33%)</t>
+          <t>Orks (36%), T'au Empire (34%)</t>
         </is>
       </c>
     </row>
